--- a/AAII_Financials/Yearly/KOS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KOS_YR_FIN.xlsx
@@ -1251,16 +1251,16 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>33300</v>
+        <v>33100</v>
       </c>
       <c r="E20" s="3">
-        <v>33400</v>
+        <v>33100</v>
       </c>
       <c r="F20" s="3">
         <v>31900</v>
       </c>
       <c r="G20" s="3">
-        <v>27400</v>
+        <v>24100</v>
       </c>
       <c r="H20" s="3">
         <v>11200</v>
@@ -1302,16 +1302,16 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>425200</v>
+        <v>425400</v>
       </c>
       <c r="E21" s="3">
-        <v>895800</v>
+        <v>896100</v>
       </c>
       <c r="F21" s="3">
         <v>1109000</v>
       </c>
       <c r="G21" s="3">
-        <v>1315400</v>
+        <v>1318700</v>
       </c>
       <c r="H21" s="3">
         <v>539400</v>
@@ -1353,16 +1353,16 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>212600</v>
+        <v>212800</v>
       </c>
       <c r="E22" s="3">
-        <v>45400</v>
+        <v>45700</v>
       </c>
       <c r="F22" s="3">
         <v>72100</v>
       </c>
       <c r="G22" s="3">
-        <v>92400</v>
+        <v>95700</v>
       </c>
       <c r="H22" s="3">
         <v>97200</v>
@@ -1863,16 +1863,16 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-33300</v>
+        <v>-33100</v>
       </c>
       <c r="E32" s="3">
-        <v>-33400</v>
+        <v>-33100</v>
       </c>
       <c r="F32" s="3">
         <v>-31900</v>
       </c>
       <c r="G32" s="3">
-        <v>-27400</v>
+        <v>-24100</v>
       </c>
       <c r="H32" s="3">
         <v>-11200</v>
